--- a/docs/session-changelog.xlsx
+++ b/docs/session-changelog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Clients\Priyam\FiveCrux\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8606A3D2-0583-4E84-95B8-288570405690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7089D241-3098-4D5A-9A0F-8DE9C62406DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" xr2:uid="{E9E1534B-C991-495F-AE32-06FC689859A5}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" xr2:uid="{E9E1534B-C991-495F-AE32-06FC689859A5}"/>
   </bookViews>
   <sheets>
     <sheet name="Fixes &amp; Changes" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="122">
   <si>
     <t>FiveCrux  -  Website Fixes &amp; Changes</t>
   </si>
@@ -33,9 +33,6 @@
     <t>Prepared for client review  -  fivecrux.com</t>
   </si>
   <si>
-    <t>35 items  -  10 Features  -  17 Bug Fixes  -  8 Improvements</t>
-  </si>
-  <si>
     <t>#</t>
   </si>
   <si>
@@ -325,13 +322,82 @@
   </si>
   <si>
     <t>All new giveaways (admins included) now honestly say 'submitted - will be reviewed', and go through the same approval step.</t>
+  </si>
+  <si>
+    <t>Scripts</t>
+  </si>
+  <si>
+    <t>Newly-approved scripts sometimes never appeared in New Releases, even minutes after going live.</t>
+  </si>
+  <si>
+    <t>Root-caused it: approval was carrying over the original submission date instead of stamping the approval time, so the sort order silently excluded them. Now stamps the approval time.</t>
+  </si>
+  <si>
+    <t>Framework tags (ESX / QBCore / Qbox / etc) were flat grey text chips with no visual distinction.</t>
+  </si>
+  <si>
+    <t>Built a shared FrameworkBadge component - icon + brand color per framework - applied across every card and detail page.</t>
+  </si>
+  <si>
+    <t>Ads, Side Banners and Featured Scripts were three separate profile tabs, hard to navigate.</t>
+  </si>
+  <si>
+    <t>Consolidated into one 'My Ad Slots' section with a switcher to flip between the three types.</t>
+  </si>
+  <si>
+    <t>Scripts' label used inconsistently across admin/profile; client wanted 'Assets' terminology.</t>
+  </si>
+  <si>
+    <t>Renamed nav items, stat tiles and section headers from 'Scripts' to 'Assets' in both admin and profile.</t>
+  </si>
+  <si>
+    <t>No way to search or filter your own listed scripts/products in the profile.</t>
+  </si>
+  <si>
+    <t>Added a search bar and category dropdown to the profile 'My Assets' list.</t>
+  </si>
+  <si>
+    <t>Featured Scripts</t>
+  </si>
+  <si>
+    <t>The script-selection popup (used when filling a bought featured slot) used a mismatched grey/purple palette.</t>
+  </si>
+  <si>
+    <t>Re-themed it to the site's black/orange palette to match every other component.</t>
+  </si>
+  <si>
+    <t>Tebex Store</t>
+  </si>
+  <si>
+    <t>Importing a Tebex package submitted straight to admin approval with no chance to review it first.</t>
+  </si>
+  <si>
+    <t>Added a review modal (title / price / category / image) before submitting, across all three import entry points (all, selected, by ID).</t>
+  </si>
+  <si>
+    <t>Maps' and 'MLOs' existed as two separate, overlapping categories site-wide, meaning the same content.</t>
+  </si>
+  <si>
+    <t>Removed the duplicate from code and local seed data. The live prod category still needs a one-time DB-side merge (client to run - we don't touch prod DB directly).</t>
+  </si>
+  <si>
+    <t>Needs DB Action</t>
+  </si>
+  <si>
+    <t>The 'multiple creator Discord IDs' feature's DB migration was never generated/committed, silently breaking local dev testing.</t>
+  </si>
+  <si>
+    <t>Generated the missing migration for local testing. Confirmed (read-only) production already has the column, so no prod action is needed.</t>
+  </si>
+  <si>
+    <t>44 items  -  12 Features  -  21 Bug Fixes  -  11 Improvements</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -400,6 +466,29 @@
     <font>
       <sz val="10"/>
       <color rgb="FFC9C2B8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF8A8F98"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -500,20 +589,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -568,6 +645,51 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1329,6 +1451,506 @@
         <a:xfrm>
           <a:off x="10480040" y="24988520"/>
           <a:ext cx="1143000" cy="711200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>38101</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1112520</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>723901</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{534F5ABD-B098-9DC5-2801-625EE065BECD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9342120" y="28811221"/>
+          <a:ext cx="1074420" cy="685800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>38101</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1112520</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>723901</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{780878FA-124F-353C-93A6-75D6BC9322B9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10492740" y="28811221"/>
+          <a:ext cx="1074420" cy="685800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>38101</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1112520</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>723901</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Picture 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10F749C0-1DE3-1864-302A-F6C6EDFB6240}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9342120" y="29573221"/>
+          <a:ext cx="1074420" cy="685800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>38101</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1112520</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>723901</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="Picture 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{719DFADE-BFCA-7851-3482-E482F7F0BE88}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10492740" y="29573221"/>
+          <a:ext cx="1074420" cy="685800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>38101</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1112520</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>723901</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="Picture 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87F3729E-4222-502A-9D62-68F2B77A6FE9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9342120" y="30335221"/>
+          <a:ext cx="1074420" cy="685800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>38101</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1112520</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>723901</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="Picture 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D749B3A5-41BC-1B55-44DE-BBC859F895EE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10492740" y="30335221"/>
+          <a:ext cx="1074420" cy="685800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>38101</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1112520</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>723901</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="28" name="Picture 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74BFB4D9-6D9D-94B4-DFCA-C579F332B670}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9342120" y="31097221"/>
+          <a:ext cx="1074420" cy="685800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>38101</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1112520</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>723901</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="32" name="Picture 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE18BC18-A301-4A35-4339-69B962047DD2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10492740" y="31097221"/>
+          <a:ext cx="1074420" cy="685800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>38101</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1112520</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>723901</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="34" name="Picture 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBD6F6D9-9694-34F5-8A16-2631D5B3A4D8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9342120" y="33383221"/>
+          <a:ext cx="1074420" cy="685800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>38101</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1112520</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>723901</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="36" name="Picture 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39D38FFC-A05C-E0C6-C22C-16ECC89A2394}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10492740" y="33383221"/>
+          <a:ext cx="1074420" cy="685800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1637,7 +2259,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1F609A6-E1DC-48C7-B847-60D5C7C74FFA}">
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.77734375" customWidth="1"/>
@@ -1649,945 +2271,1159 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
     </row>
     <row r="2" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
     </row>
     <row r="3" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+    </row>
+    <row r="4" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-    </row>
-    <row r="4" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="F4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="H4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="5" t="s">
+    </row>
+    <row r="5" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="7">
-        <v>1</v>
-      </c>
-      <c r="B5" s="8" t="s">
+      <c r="C5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="E5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="12" t="s">
+      <c r="F5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="9">
+        <v>2</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="D6" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+    </row>
+    <row r="8" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="9">
+        <v>4</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="11" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="13">
-        <v>2</v>
-      </c>
-      <c r="B6" s="14" t="s">
+      <c r="D9" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="9">
+        <v>6</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="16"/>
+    </row>
+    <row r="11" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="9">
+        <v>8</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+    </row>
+    <row r="13" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+    </row>
+    <row r="14" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="9">
+        <v>10</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="D14" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="9">
+        <v>12</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <v>13</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="9">
+        <v>14</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
+        <v>15</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="9">
+        <v>16</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
         <v>17</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="B21" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" s="15"/>
+      <c r="H21" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="9">
         <v>18</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="B22" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="17" t="s">
+      <c r="D22" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" s="16"/>
+      <c r="H22" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <v>19</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" s="15"/>
+      <c r="H23" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="9">
+        <v>20</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <v>21</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="9">
+        <v>22</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C26" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="17" t="s">
+      <c r="D26" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H26" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <v>23</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+    </row>
+    <row r="28" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="9">
+        <v>24</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <v>25</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="11" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="7">
-        <v>3</v>
-      </c>
-      <c r="B7" s="8" t="s">
+      <c r="D29" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="9">
+        <v>26</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <v>27</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="9">
+        <v>28</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-    </row>
-    <row r="8" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="13">
-        <v>4</v>
-      </c>
-      <c r="B8" s="14" t="s">
+      <c r="D32" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G32" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H32" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <v>29</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="9">
+        <v>30</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C34" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" s="17" t="s">
+      <c r="D34" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G34" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H34" s="16"/>
+    </row>
+    <row r="35" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <v>31</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H35" s="15"/>
+    </row>
+    <row r="36" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="9">
+        <v>32</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="E36" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G36" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" s="16"/>
+    </row>
+    <row r="37" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <v>33</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="9">
+        <v>34</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G38" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H38" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
+        <v>35</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H39" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="24">
+        <v>36</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C40" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="E40" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="F40" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G40" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H40" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="29">
+        <v>37</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C41" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="17" t="s">
+      <c r="D41" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="E41" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="F41" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G41" s="28"/>
+      <c r="H41" s="28"/>
+    </row>
+    <row r="42" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="24">
+        <v>38</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C42" s="30" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="7">
-        <v>5</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" s="12" t="s">
+      <c r="D42" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="E42" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="F42" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G42" s="23"/>
+      <c r="H42" s="23"/>
+    </row>
+    <row r="43" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="29">
+        <v>39</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C43" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="13">
-        <v>6</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="H10" s="20"/>
-    </row>
-    <row r="11" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="7">
-        <v>7</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H11" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="13">
-        <v>8</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20"/>
-    </row>
-    <row r="13" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="7">
-        <v>9</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E13" s="10" t="s">
+      <c r="D43" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="E43" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="F43" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G43" s="28"/>
+      <c r="H43" s="28"/>
+    </row>
+    <row r="44" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="24">
+        <v>40</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C44" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="E44" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="F44" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G44" s="23"/>
+      <c r="H44" s="23"/>
+    </row>
+    <row r="45" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="29">
+        <v>41</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C45" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="D45" s="31" t="s">
+        <v>111</v>
+      </c>
+      <c r="E45" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="F45" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="24">
+        <v>42</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="C46" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="E46" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="F46" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G46" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H46" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="29">
+        <v>43</v>
+      </c>
+      <c r="B47" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F13" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-    </row>
-    <row r="14" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="13">
-        <v>10</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="H14" s="17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="7">
-        <v>11</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H15" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="13">
-        <v>12</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="16" t="s">
+      <c r="C47" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="D47" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="E47" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="F47" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="G47" s="28"/>
+      <c r="H47" s="28"/>
+    </row>
+    <row r="48" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="24">
         <v>44</v>
       </c>
-      <c r="E16" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="H16" s="17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="7">
-        <v>13</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H17" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="13">
-        <v>14</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G18" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="H18" s="17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="7">
-        <v>15</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H19" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="13">
-        <v>16</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D20" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E20" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G20" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="H20" s="17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="7">
-        <v>17</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C21" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="D21" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G21" s="19"/>
-      <c r="H21" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="13">
-        <v>18</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C22" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="E22" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22" s="20"/>
-      <c r="H22" s="17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="7">
+      <c r="B48" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C48" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G23" s="19"/>
-      <c r="H23" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="13">
-        <v>20</v>
-      </c>
-      <c r="B24" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C24" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="D24" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="E24" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G24" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="H24" s="17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="7">
-        <v>21</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C25" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="F25" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G25" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H25" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="13">
-        <v>22</v>
-      </c>
-      <c r="B26" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D26" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="E26" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="F26" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G26" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="H26" s="17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="7">
-        <v>23</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="F27" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
-    </row>
-    <row r="28" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="13">
-        <v>24</v>
-      </c>
-      <c r="B28" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C28" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="E28" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="F28" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G28" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="H28" s="17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="7">
-        <v>25</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="F29" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="G29" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H29" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="13">
-        <v>26</v>
-      </c>
-      <c r="B30" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D30" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="E30" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="F30" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G30" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="H30" s="17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="7">
-        <v>27</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C31" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="E31" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="F31" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G31" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H31" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="13">
-        <v>28</v>
-      </c>
-      <c r="B32" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D32" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="E32" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="F32" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G32" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="H32" s="17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="7">
-        <v>29</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C33" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="E33" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="F33" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G33" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H33" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="13">
-        <v>30</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D34" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="E34" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="F34" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G34" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="H34" s="20"/>
-    </row>
-    <row r="35" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="7">
-        <v>31</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="F35" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G35" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H35" s="19"/>
-    </row>
-    <row r="36" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="13">
-        <v>32</v>
-      </c>
-      <c r="B36" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D36" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="E36" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="F36" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G36" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="H36" s="20"/>
-    </row>
-    <row r="37" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="7">
-        <v>33</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="F37" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G37" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H37" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="13">
-        <v>34</v>
-      </c>
-      <c r="B38" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="C38" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="D38" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="E38" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="F38" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G38" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="H38" s="17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="7">
-        <v>35</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="C39" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="D39" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="E39" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="F39" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G39" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H39" s="12" t="s">
-        <v>16</v>
+      <c r="D48" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="E48" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="F48" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G48" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H48" s="13" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/docs/session-changelog.xlsx
+++ b/docs/session-changelog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Clients\Priyam\FiveCrux\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7089D241-3098-4D5A-9A0F-8DE9C62406DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC28C77E-5298-49B6-8930-371C3EEC671B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" xr2:uid="{E9E1534B-C991-495F-AE32-06FC689859A5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E9E1534B-C991-495F-AE32-06FC689859A5}"/>
   </bookViews>
   <sheets>
     <sheet name="Fixes &amp; Changes" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="135">
   <si>
     <t>FiveCrux  -  Website Fixes &amp; Changes</t>
   </si>
@@ -390,7 +390,46 @@
     <t>Generated the missing migration for local testing. Confirmed (read-only) production already has the column, so no prod action is needed.</t>
   </si>
   <si>
-    <t>44 items  -  12 Features  -  21 Bug Fixes  -  11 Improvements</t>
+    <t>Coupons/Creator Codes management lived on FiveCrux's own database, disconnected from the real Tebex checkout.</t>
+  </si>
+  <si>
+    <t>Switched coupon validation to check directly against Tebex; removed the now-redundant local coupon/creator-code management from the profile (kept in code, just disabled, in case it's needed again).</t>
+  </si>
+  <si>
+    <t>Ad Slots</t>
+  </si>
+  <si>
+    <t>The 'Create New Ad' and file-upload forms still used an old grey theme that didn't match the rest of the site.</t>
+  </si>
+  <si>
+    <t>Rethemed both forms (and the Props tab cards) to the site's black/orange look.</t>
+  </si>
+  <si>
+    <t>Admin Dashboard</t>
+  </si>
+  <si>
+    <t>Admins had no way to search or filter the Assets/Props/Giveaways/Ads lists in the admin dashboard - had to scroll through everything.</t>
+  </si>
+  <si>
+    <t>Added a search box plus category/status filters to all four admin dashboard tabs, and to the profile's Props tab.</t>
+  </si>
+  <si>
+    <t>The 'Buy Slot' cards under My Ad Slots &gt; Featured Scripts used a mismatched purple/pink color scheme, unlike every other tab.</t>
+  </si>
+  <si>
+    <t>Rethemed to the site's orange, matching Ads/Props/Assets.</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>A full security audit found several ways a logged-in account could act outside its own listings: edit or delete another seller's script/giveaway, mark a giveaway as 'Featured' for free, create an ad slot without actually buying one, or inflate giveaway-entry points by faking a Discord-join.</t>
+  </si>
+  <si>
+    <t>Closed all of the above: ownership checks added everywhere they were missing, 'Featured' is now admin-only, ad/slot purchases are verified server-side, and Discord-join claims are re-checked before awarding points.</t>
+  </si>
+  <si>
+    <t>49 items  -  13 Features  -  24 Bug Fixes  -  12 Improvements</t>
   </si>
 </sst>
 </file>
@@ -645,18 +684,6 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -689,6 +716,18 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2259,7 +2298,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1F609A6-E1DC-48C7-B847-60D5C7C74FFA}">
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.77734375" customWidth="1"/>
@@ -2271,40 +2310,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
     </row>
     <row r="2" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
     </row>
     <row r="3" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
+      <c r="A3" s="33" t="s">
+        <v>134</v>
+      </c>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
     </row>
     <row r="4" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -3213,22 +3252,22 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="24">
+      <c r="A40" s="20">
         <v>36</v>
       </c>
       <c r="B40" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="C40" s="25" t="s">
+      <c r="C40" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="D40" s="26" t="s">
+      <c r="D40" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="E40" s="26" t="s">
+      <c r="E40" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="F40" s="27" t="s">
+      <c r="F40" s="23" t="s">
         <v>14</v>
       </c>
       <c r="G40" s="13" t="s">
@@ -3239,110 +3278,110 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="29">
+      <c r="A41" s="25">
         <v>37</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C41" s="30" t="s">
+      <c r="C41" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="D41" s="31" t="s">
+      <c r="D41" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="E41" s="31" t="s">
+      <c r="E41" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="F41" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="G41" s="28"/>
-      <c r="H41" s="28"/>
+      <c r="F41" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G41" s="24"/>
+      <c r="H41" s="24"/>
     </row>
     <row r="42" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="24">
+      <c r="A42" s="20">
         <v>38</v>
       </c>
       <c r="B42" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C42" s="30" t="s">
+      <c r="C42" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="D42" s="26" t="s">
+      <c r="D42" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="E42" s="26" t="s">
+      <c r="E42" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="F42" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="G42" s="23"/>
-      <c r="H42" s="23"/>
+      <c r="F42" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G42" s="19"/>
+      <c r="H42" s="19"/>
     </row>
     <row r="43" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="29">
+      <c r="A43" s="25">
         <v>39</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C43" s="30" t="s">
+      <c r="C43" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="D43" s="32" t="s">
+      <c r="D43" s="28" t="s">
         <v>106</v>
       </c>
-      <c r="E43" s="31" t="s">
+      <c r="E43" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="F43" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="G43" s="28"/>
-      <c r="H43" s="28"/>
+      <c r="F43" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G43" s="24"/>
+      <c r="H43" s="24"/>
     </row>
     <row r="44" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="24">
+      <c r="A44" s="20">
         <v>40</v>
       </c>
       <c r="B44" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C44" s="33" t="s">
+      <c r="C44" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="D44" s="26" t="s">
+      <c r="D44" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="E44" s="26" t="s">
+      <c r="E44" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="F44" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="G44" s="23"/>
-      <c r="H44" s="23"/>
+      <c r="F44" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G44" s="19"/>
+      <c r="H44" s="19"/>
     </row>
     <row r="45" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="29">
+      <c r="A45" s="25">
         <v>41</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="C45" s="25" t="s">
+      <c r="C45" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="D45" s="31" t="s">
+      <c r="D45" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="E45" s="31" t="s">
+      <c r="E45" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="F45" s="27" t="s">
+      <c r="F45" s="23" t="s">
         <v>14</v>
       </c>
       <c r="G45" s="8" t="s">
@@ -3353,22 +3392,22 @@
       </c>
     </row>
     <row r="46" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="24">
+      <c r="A46" s="20">
         <v>42</v>
       </c>
       <c r="B46" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="C46" s="33" t="s">
+      <c r="C46" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="D46" s="26" t="s">
+      <c r="D46" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="E46" s="26" t="s">
+      <c r="E46" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="F46" s="27" t="s">
+      <c r="F46" s="23" t="s">
         <v>14</v>
       </c>
       <c r="G46" s="13" t="s">
@@ -3379,50 +3418,180 @@
       </c>
     </row>
     <row r="47" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="29">
+      <c r="A47" s="25">
         <v>43</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C47" s="25" t="s">
+      <c r="C47" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="D47" s="32" t="s">
+      <c r="D47" s="28" t="s">
         <v>116</v>
       </c>
-      <c r="E47" s="31" t="s">
+      <c r="E47" s="27" t="s">
         <v>117</v>
       </c>
-      <c r="F47" s="30" t="s">
+      <c r="F47" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="G47" s="28"/>
-      <c r="H47" s="28"/>
+      <c r="G47" s="24"/>
+      <c r="H47" s="24"/>
     </row>
     <row r="48" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="24">
+      <c r="A48" s="20">
         <v>44</v>
       </c>
       <c r="B48" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="C48" s="25" t="s">
+      <c r="C48" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="D48" s="26" t="s">
+      <c r="D48" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="E48" s="26" t="s">
+      <c r="E48" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="F48" s="27" t="s">
+      <c r="F48" s="23" t="s">
         <v>14</v>
       </c>
       <c r="G48" s="13" t="s">
         <v>15</v>
       </c>
       <c r="H48" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A49" s="25">
+        <v>45</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C49" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="D49" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="E49" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="F49" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G49" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="H49" s="24" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A50" s="20">
+        <v>46</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C50" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D50" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="E50" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="F50" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G50" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H50" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A51" s="25">
+        <v>47</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C51" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D51" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="E51" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="F51" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G51" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="H51" s="24" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A52" s="20">
+        <v>48</v>
+      </c>
+      <c r="B52" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="C52" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D52" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="E52" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="F52" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G52" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H52" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="25">
+        <v>49</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C53" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D53" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="E53" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="F53" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G53" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="H53" s="24" t="s">
         <v>15</v>
       </c>
     </row>
